--- a/02_Groups/Proteome_training/c_data/clustering.xlsx
+++ b/02_Groups/Proteome_training/c_data/clustering.xlsx
@@ -211,10 +211,10 @@
     <t>Participant identifier.</t>
   </si>
   <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
+    <t>hr_lr</t>
+  </si>
+  <si>
+    <t>The study's HR or LR label, shown beside a cluster grouping's own group.</t>
   </si>
   <si>
     <t>k2</t>
@@ -355,7 +355,7 @@
     <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
   </si>
   <si>
-    <t>9062a97ff96fac52908895e0eeb7bf57</t>
+    <t>37335a295505b53dcf355baf87333202</t>
   </si>
   <si>
     <t>phenotype</t>
@@ -364,7 +364,7 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>BiocGenerics</t>
